--- a/models/kimi-k3-dspark/kimi-k3-dspark-analysis.xlsx
+++ b/models/kimi-k3-dspark/kimi-k3-dspark-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R1aec05dc1b2d458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R8d075b9e37a645be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R070dcea449ad466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rc7bfa200ed554920"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,13 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00%"/>
+    <x:numFmt numFmtId="207" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +45,14 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +72,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -99,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,10 +197,71 @@
     <x:xf numFmtId="201" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -2135,7 +2221,877 @@
       <x:c r="O37" s="30"/>
       <x:c r="P37" s="30"/>
     </x:row>
+    <x:row r="70" ht="23" customHeight="1">
+      <x:c r="A70" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B70" s="30"/>
+      <x:c r="C70" s="30"/>
+      <x:c r="D70" s="30"/>
+      <x:c r="E70" s="30"/>
+      <x:c r="F70" s="30"/>
+      <x:c r="G70" s="30"/>
+      <x:c r="H70" s="30"/>
+      <x:c r="I70" s="30"/>
+      <x:c r="J70" s="30"/>
+      <x:c r="K70" s="30"/>
+      <x:c r="L70" s="30"/>
+    </x:row>
+    <x:row r="71" ht="23" customHeight="1">
+      <x:c r="A71" s="30" t="str">
+        <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B71" s="30"/>
+      <x:c r="C71" s="30"/>
+      <x:c r="D71" s="30"/>
+      <x:c r="E71" s="30"/>
+      <x:c r="F71" s="30"/>
+      <x:c r="G71" s="30"/>
+      <x:c r="H71" s="30"/>
+      <x:c r="I71" s="30"/>
+      <x:c r="J71" s="30"/>
+      <x:c r="K71" s="30"/>
+      <x:c r="L71" s="30"/>
+    </x:row>
+    <x:row r="72" ht="38" customHeight="1">
+      <x:c r="A72" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C72" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E72" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F72" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G72" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I72" s="30"/>
+      <x:c r="J72" s="30"/>
+      <x:c r="K72" s="30"/>
+      <x:c r="L72" s="30"/>
+    </x:row>
+    <x:row r="73" ht="23" customHeight="1">
+      <x:c r="A73" s="30"/>
+      <x:c r="B73" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C73" s="30"/>
+      <x:c r="D73" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" s="30"/>
+      <x:c r="F73" s="48"/>
+      <x:c r="G73" s="30"/>
+      <x:c r="H73" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I73" s="30"/>
+      <x:c r="J73" s="30"/>
+      <x:c r="K73" s="30"/>
+      <x:c r="L73" s="30"/>
+    </x:row>
+    <x:row r="74" ht="38" customHeight="1">
+      <x:c r="A74" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C74" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E74" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G74" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I74" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K74" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L74" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="23" customHeight="1">
+      <x:c r="A75" s="49"/>
+      <x:c r="B75" s="49" t="n">
+        <x:f>SUM(G79:G92)</x:f>
+        <x:v>13.629521919999998</x:v>
+      </x:c>
+      <x:c r="C75" s="49"/>
+      <x:c r="D75" s="49" t="n">
+        <x:f>SUM(H79:H92)</x:f>
+        <x:v>15.143913244444445</x:v>
+      </x:c>
+      <x:c r="E75" s="49"/>
+      <x:c r="F75" s="49" t="n">
+        <x:f>SUM(K79:K92)</x:f>
+        <x:v>1.5143913244444445</x:v>
+      </x:c>
+      <x:c r="G75" s="49"/>
+      <x:c r="H75" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G92,J79:J92)),$F$73+F75,"")</x:f>
+      </x:c>
+      <x:c r="I75" s="49"/>
+      <x:c r="J75" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G92,J79:J92)),F75/$F$73,"")</x:f>
+      </x:c>
+      <x:c r="K75" s="49"/>
+      <x:c r="L75" s="49" t="str">
+        <x:f>IF($F$73="","待填基线",IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G92,J79:J92)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="23" customHeight="1">
+      <x:c r="A76" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B76" s="30"/>
+      <x:c r="C76" s="30"/>
+      <x:c r="D76" s="30"/>
+      <x:c r="E76" s="30"/>
+      <x:c r="F76" s="30"/>
+      <x:c r="G76" s="30"/>
+      <x:c r="H76" s="30"/>
+      <x:c r="I76" s="30"/>
+      <x:c r="J76" s="30"/>
+      <x:c r="K76" s="30"/>
+      <x:c r="L76" s="30"/>
+    </x:row>
+    <x:row r="77" ht="23" customHeight="1">
+      <x:c r="A77" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B77" s="30"/>
+      <x:c r="C77" s="30"/>
+      <x:c r="D77" s="30"/>
+      <x:c r="E77" s="30"/>
+      <x:c r="F77" s="30"/>
+      <x:c r="G77" s="30"/>
+      <x:c r="H77" s="30"/>
+      <x:c r="I77" s="30"/>
+      <x:c r="J77" s="30"/>
+      <x:c r="K77" s="30"/>
+      <x:c r="L77" s="30"/>
+    </x:row>
+    <x:row r="78" ht="38" customHeight="1">
+      <x:c r="A78" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B78" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C78" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D78" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E78" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F78" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G78" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H78" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I78" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J78" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K78" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L78" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="23" customHeight="1">
+      <x:c r="A79" s="30" t="str">
+        <x:v>TP</x:v>
+      </x:c>
+      <x:c r="B79" s="30" t="str">
+        <x:v>Input Projection</x:v>
+      </x:c>
+      <x:c r="C79" s="30" t="str">
+        <x:v>Column Parallel 输出</x:v>
+      </x:c>
+      <x:c r="D79" s="34" t="n">
+        <x:f>(K23*2^20)/1e9</x:f>
+        <x:v>0.102760448</x:v>
+      </x:c>
+      <x:c r="E79" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F79" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E79),E79&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F79),F79&gt;=0,F79&lt;=1,ISNUMBER(J79),J79&gt;=0,J79&lt;=1),D79/E79*1000,NA())</x:f>
+        <x:v>1.0276044800000002</x:v>
+      </x:c>
+      <x:c r="H79" s="34" t="n">
+        <x:f>G79+I79</x:f>
+        <x:v>1.1417827555555558</x:v>
+      </x:c>
+      <x:c r="I79" s="34" t="n">
+        <x:f>G79*F79*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="J79" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K79" s="34" t="n">
+        <x:f>I79*J79</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="L79" s="30" t="str">
+        <x:v>原通信行 23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="23" customHeight="1">
+      <x:c r="A80" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B80" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C80" s="30" t="str">
+        <x:v>Attention 前</x:v>
+      </x:c>
+      <x:c r="D80" s="34" t="n">
+        <x:f>(K24*2^20)/1e9</x:f>
+        <x:v>0.51380224</x:v>
+      </x:c>
+      <x:c r="E80" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F80" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E80),E80&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F80),F80&gt;=0,F80&lt;=1,ISNUMBER(J80),J80&gt;=0,J80&lt;=1),D80/E80*1000,NA())</x:f>
+        <x:v>5.1380224</x:v>
+      </x:c>
+      <x:c r="H80" s="34" t="n">
+        <x:f>G80+I80</x:f>
+        <x:v>5.708913777777777</x:v>
+      </x:c>
+      <x:c r="I80" s="34" t="n">
+        <x:f>G80*F80*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.5708913777777778</x:v>
+      </x:c>
+      <x:c r="J80" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K80" s="34" t="n">
+        <x:f>I80*J80</x:f>
+        <x:v>0.5708913777777778</x:v>
+      </x:c>
+      <x:c r="L80" s="30" t="str">
+        <x:v>原通信行 24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="23" customHeight="1">
+      <x:c r="A81" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B81" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C81" s="30" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D81" s="34" t="n">
+        <x:f>(K25*2^20)/1e9</x:f>
+        <x:v>0.51380224</x:v>
+      </x:c>
+      <x:c r="E81" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F81" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E81),E81&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F81),F81&gt;=0,F81&lt;=1,ISNUMBER(J81),J81&gt;=0,J81&lt;=1),D81/E81*1000,NA())</x:f>
+        <x:v>5.1380224</x:v>
+      </x:c>
+      <x:c r="H81" s="34" t="n">
+        <x:f>G81+I81</x:f>
+        <x:v>5.708913777777777</x:v>
+      </x:c>
+      <x:c r="I81" s="34" t="n">
+        <x:f>G81*F81*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.5708913777777778</x:v>
+      </x:c>
+      <x:c r="J81" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K81" s="34" t="n">
+        <x:f>I81*J81</x:f>
+        <x:v>0.5708913777777778</x:v>
+      </x:c>
+      <x:c r="L81" s="30" t="str">
+        <x:v>原通信行 25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="23" customHeight="1">
+      <x:c r="A82" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B82" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C82" s="30" t="str">
+        <x:v>非 SP 标准 TP</x:v>
+      </x:c>
+      <x:c r="D82" s="34" t="n">
+        <x:f>(K26*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E82" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F82" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E82),E82&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F82),F82&gt;=0,F82&lt;=1,ISNUMBER(J82),J82&gt;=0,J82&lt;=1),D82/E82*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="34" t="n">
+        <x:f>G82+I82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82" s="34" t="n">
+        <x:f>G82*F82*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K82" s="34" t="n">
+        <x:f>I82*J82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82" s="30" t="str">
+        <x:v>原通信行 26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="23" customHeight="1">
+      <x:c r="A83" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B83" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C83" s="30" t="str">
+        <x:v>O Proj 输入</x:v>
+      </x:c>
+      <x:c r="D83" s="34" t="n">
+        <x:f>(K27*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E83" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F83" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E83),E83&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F83),F83&gt;=0,F83&lt;=1,ISNUMBER(J83),J83&gt;=0,J83&lt;=1),D83/E83*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="34" t="n">
+        <x:f>G83+I83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83" s="34" t="n">
+        <x:f>G83*F83*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J83" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K83" s="34" t="n">
+        <x:f>I83*J83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="30" t="str">
+        <x:v>原通信行 27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="23" customHeight="1">
+      <x:c r="A84" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B84" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="str">
+        <x:v>O Proj 输出</x:v>
+      </x:c>
+      <x:c r="D84" s="34" t="n">
+        <x:f>(K28*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E84" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F84" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E84),E84&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F84),F84&gt;=0,F84&lt;=1,ISNUMBER(J84),J84&gt;=0,J84&lt;=1),D84/E84*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="34" t="n">
+        <x:f>G84+I84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" s="34" t="n">
+        <x:f>G84*F84*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J84" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K84" s="34" t="n">
+        <x:f>I84*J84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L84" s="30" t="str">
+        <x:v>原通信行 28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="23" customHeight="1">
+      <x:c r="A85" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B85" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C85" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D85" s="34" t="n">
+        <x:f>(K29*2^20)/1e9</x:f>
+        <x:v>0.12845056</x:v>
+      </x:c>
+      <x:c r="E85" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F85" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E85),E85&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F85),F85&gt;=0,F85&lt;=1,ISNUMBER(J85),J85&gt;=0,J85&lt;=1),D85/E85*1000,NA())</x:f>
+        <x:v>1.2845056</x:v>
+      </x:c>
+      <x:c r="H85" s="34" t="n">
+        <x:f>G85+I85</x:f>
+        <x:v>1.4272284444444443</x:v>
+      </x:c>
+      <x:c r="I85" s="34" t="n">
+        <x:f>G85*F85*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.14272284444444444</x:v>
+      </x:c>
+      <x:c r="J85" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K85" s="34" t="n">
+        <x:f>I85*J85</x:f>
+        <x:v>0.14272284444444444</x:v>
+      </x:c>
+      <x:c r="L85" s="30" t="str">
+        <x:v>原通信行 29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="23" customHeight="1">
+      <x:c r="A86" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B86" s="30" t="str">
+        <x:v>Attention KV</x:v>
+      </x:c>
+      <x:c r="C86" s="30" t="str">
+        <x:v>KV Cache 写入前</x:v>
+      </x:c>
+      <x:c r="D86" s="34" t="n">
+        <x:f>(K30*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E86" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F86" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E86),E86&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F86),F86&gt;=0,F86&lt;=1,ISNUMBER(J86),J86&gt;=0,J86&lt;=1),D86/E86*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="34" t="n">
+        <x:f>G86+I86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86" s="34" t="n">
+        <x:f>G86*F86*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J86" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" s="34" t="n">
+        <x:f>I86*J86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="30" t="str">
+        <x:v>原通信行 30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="23" customHeight="1">
+      <x:c r="A87" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B87" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C87" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D87" s="34" t="n">
+        <x:f>(K31*2^20)/1e9</x:f>
+        <x:v>0.102760448</x:v>
+      </x:c>
+      <x:c r="E87" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E87),E87&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F87),F87&gt;=0,F87&lt;=1,ISNUMBER(J87),J87&gt;=0,J87&lt;=1),D87/E87*1000,NA())</x:f>
+        <x:v>1.0276044800000002</x:v>
+      </x:c>
+      <x:c r="H87" s="34" t="n">
+        <x:f>G87+I87</x:f>
+        <x:v>1.1417827555555558</x:v>
+      </x:c>
+      <x:c r="I87" s="34" t="n">
+        <x:f>G87*F87*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="J87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K87" s="34" t="n">
+        <x:f>I87*J87</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="L87" s="30" t="str">
+        <x:v>原通信行 31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="23" customHeight="1">
+      <x:c r="A88" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B88" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C88" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D88" s="34" t="n">
+        <x:f>(K32*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E88" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E88),E88&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F88),F88&gt;=0,F88&lt;=1,ISNUMBER(J88),J88&gt;=0,J88&lt;=1),D88/E88*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="34" t="n">
+        <x:f>G88+I88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="34" t="n">
+        <x:f>G88*F88*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K88" s="34" t="n">
+        <x:f>I88*J88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="30" t="str">
+        <x:v>原通信行 32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="23" customHeight="1">
+      <x:c r="A89" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B89" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C89" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D89" s="34" t="n">
+        <x:f>(K33*2^20)/1e9</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="E89" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E89),E89&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F89),F89&gt;=0,F89&lt;=1,ISNUMBER(J89),J89&gt;=0,J89&lt;=1),D89/E89*1000,NA())</x:f>
+        <x:v>0.01376256</x:v>
+      </x:c>
+      <x:c r="H89" s="34" t="n">
+        <x:f>G89+I89</x:f>
+        <x:v>0.015291733333333333</x:v>
+      </x:c>
+      <x:c r="I89" s="34" t="n">
+        <x:f>G89*F89*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="J89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K89" s="34" t="n">
+        <x:f>I89*J89</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="L89" s="30" t="str">
+        <x:v>原通信行 33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="23" customHeight="1">
+      <x:c r="A90" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B90" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C90" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D90" s="34" t="n">
+        <x:f>(K34*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E90" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E90),E90&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F90),F90&gt;=0,F90&lt;=1,ISNUMBER(J90),J90&gt;=0,J90&lt;=1),D90/E90*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="34" t="n">
+        <x:f>G90+I90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" s="34" t="n">
+        <x:f>G90*F90*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K90" s="34" t="n">
+        <x:f>I90*J90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" s="30" t="str">
+        <x:v>原通信行 34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="23" customHeight="1">
+      <x:c r="A91" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B91" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D91" s="34" t="n">
+        <x:f>(K35*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E91" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E91),E91&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F91),F91&gt;=0,F91&lt;=1,ISNUMBER(J91),J91&gt;=0,J91&lt;=1),D91/E91*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="34" t="n">
+        <x:f>G91+I91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I91" s="34" t="n">
+        <x:f>G91*F91*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K91" s="34" t="n">
+        <x:f>I91*J91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" s="30" t="str">
+        <x:v>原通信行 35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="23" customHeight="1">
+      <x:c r="A92" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B92" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D92" s="34" t="n">
+        <x:f>(K36*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E92" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E92),E92&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F92),F92&gt;=0,F92&lt;=1,ISNUMBER(J92),J92&gt;=0,J92&lt;=1),D92/E92*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="34" t="n">
+        <x:f>G92+I92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I92" s="34" t="n">
+        <x:f>G92*F92*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K92" s="34" t="n">
+        <x:f>I92*J92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L92" s="30" t="str">
+        <x:v>原通信行 36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="23" customHeight="1">
+      <x:c r="A93" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B93" s="53"/>
+      <x:c r="C93" s="53"/>
+      <x:c r="D93" s="54" t="n">
+        <x:f>SUM(D79:D92)</x:f>
+        <x:v>1.3629521919999996</x:v>
+      </x:c>
+      <x:c r="E93" s="54"/>
+      <x:c r="F93" s="53"/>
+      <x:c r="G93" s="54" t="n">
+        <x:f>SUM(G79:G92)</x:f>
+        <x:v>13.629521919999998</x:v>
+      </x:c>
+      <x:c r="H93" s="54" t="n">
+        <x:f>SUM(H79:H92)</x:f>
+        <x:v>15.143913244444445</x:v>
+      </x:c>
+      <x:c r="I93" s="54" t="n">
+        <x:f>SUM(I79:I92)</x:f>
+        <x:v>1.5143913244444445</x:v>
+      </x:c>
+      <x:c r="J93" s="53"/>
+      <x:c r="K93" s="54" t="n">
+        <x:f>SUM(K79:K92)</x:f>
+        <x:v>1.5143913244444445</x:v>
+      </x:c>
+      <x:c r="L93" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L75:L75">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -4005,7 +4961,965 @@
       <x:c r="O39" s="30"/>
       <x:c r="P39" s="30"/>
     </x:row>
+    <x:row r="70" ht="23" customHeight="1">
+      <x:c r="A70" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B70" s="30"/>
+      <x:c r="C70" s="30"/>
+      <x:c r="D70" s="30"/>
+      <x:c r="E70" s="30"/>
+      <x:c r="F70" s="30"/>
+      <x:c r="G70" s="30"/>
+      <x:c r="H70" s="30"/>
+      <x:c r="I70" s="30"/>
+      <x:c r="J70" s="30"/>
+      <x:c r="K70" s="30"/>
+      <x:c r="L70" s="30"/>
+    </x:row>
+    <x:row r="71" ht="23" customHeight="1">
+      <x:c r="A71" s="30" t="str">
+        <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B71" s="30"/>
+      <x:c r="C71" s="30"/>
+      <x:c r="D71" s="30"/>
+      <x:c r="E71" s="30"/>
+      <x:c r="F71" s="30"/>
+      <x:c r="G71" s="30"/>
+      <x:c r="H71" s="30"/>
+      <x:c r="I71" s="30"/>
+      <x:c r="J71" s="30"/>
+      <x:c r="K71" s="30"/>
+      <x:c r="L71" s="30"/>
+    </x:row>
+    <x:row r="72" ht="38" customHeight="1">
+      <x:c r="A72" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C72" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E72" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F72" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G72" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H72" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I72" s="30"/>
+      <x:c r="J72" s="30"/>
+      <x:c r="K72" s="30"/>
+      <x:c r="L72" s="30"/>
+    </x:row>
+    <x:row r="73" ht="23" customHeight="1">
+      <x:c r="A73" s="30"/>
+      <x:c r="B73" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C73" s="30"/>
+      <x:c r="D73" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" s="30"/>
+      <x:c r="F73" s="48"/>
+      <x:c r="G73" s="30"/>
+      <x:c r="H73" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I73" s="30"/>
+      <x:c r="J73" s="30"/>
+      <x:c r="K73" s="30"/>
+      <x:c r="L73" s="30"/>
+    </x:row>
+    <x:row r="74" ht="38" customHeight="1">
+      <x:c r="A74" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C74" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E74" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G74" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I74" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J74" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K74" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L74" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="23" customHeight="1">
+      <x:c r="A75" s="49"/>
+      <x:c r="B75" s="49" t="n">
+        <x:f>SUM(G79:G94)</x:f>
+        <x:v>1.8120703999999999</x:v>
+      </x:c>
+      <x:c r="C75" s="49"/>
+      <x:c r="D75" s="49" t="n">
+        <x:f>SUM(H79:H94)</x:f>
+        <x:v>2.0134115555555554</x:v>
+      </x:c>
+      <x:c r="E75" s="49"/>
+      <x:c r="F75" s="49" t="n">
+        <x:f>SUM(K79:K94)</x:f>
+        <x:v>0.20134115555555557</x:v>
+      </x:c>
+      <x:c r="G75" s="49"/>
+      <x:c r="H75" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G94,J79:J94)),$F$73+F75,"")</x:f>
+      </x:c>
+      <x:c r="I75" s="49"/>
+      <x:c r="J75" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G94,J79:J94)),F75/$F$73,"")</x:f>
+      </x:c>
+      <x:c r="K75" s="49"/>
+      <x:c r="L75" s="49" t="str">
+        <x:f>IF($F$73="","待填基线",IF(AND(ISNUMBER($F$73),$F$73&gt;0,$F$73&gt;=SUMPRODUCT(G79:G94,J79:J94)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="23" customHeight="1">
+      <x:c r="A76" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B76" s="30"/>
+      <x:c r="C76" s="30"/>
+      <x:c r="D76" s="30"/>
+      <x:c r="E76" s="30"/>
+      <x:c r="F76" s="30"/>
+      <x:c r="G76" s="30"/>
+      <x:c r="H76" s="30"/>
+      <x:c r="I76" s="30"/>
+      <x:c r="J76" s="30"/>
+      <x:c r="K76" s="30"/>
+      <x:c r="L76" s="30"/>
+    </x:row>
+    <x:row r="77" ht="23" customHeight="1">
+      <x:c r="A77" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B77" s="30"/>
+      <x:c r="C77" s="30"/>
+      <x:c r="D77" s="30"/>
+      <x:c r="E77" s="30"/>
+      <x:c r="F77" s="30"/>
+      <x:c r="G77" s="30"/>
+      <x:c r="H77" s="30"/>
+      <x:c r="I77" s="30"/>
+      <x:c r="J77" s="30"/>
+      <x:c r="K77" s="30"/>
+      <x:c r="L77" s="30"/>
+    </x:row>
+    <x:row r="78" ht="38" customHeight="1">
+      <x:c r="A78" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B78" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C78" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D78" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E78" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F78" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G78" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H78" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I78" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J78" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K78" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L78" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="23" customHeight="1">
+      <x:c r="A79" s="30" t="str">
+        <x:v>TP</x:v>
+      </x:c>
+      <x:c r="B79" s="30" t="str">
+        <x:v>Input Projection</x:v>
+      </x:c>
+      <x:c r="C79" s="30" t="str">
+        <x:v>Column Parallel 输出</x:v>
+      </x:c>
+      <x:c r="D79" s="34" t="n">
+        <x:f>(K23*2^20)/1e9</x:f>
+        <x:v>0.012845056</x:v>
+      </x:c>
+      <x:c r="E79" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F79" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E79),E79&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F79),F79&gt;=0,F79&lt;=1,ISNUMBER(J79),J79&gt;=0,J79&lt;=1),D79/E79*1000,NA())</x:f>
+        <x:v>0.12845056000000002</x:v>
+      </x:c>
+      <x:c r="H79" s="34" t="n">
+        <x:f>G79+I79</x:f>
+        <x:v>0.14272284444444447</x:v>
+      </x:c>
+      <x:c r="I79" s="34" t="n">
+        <x:f>G79*F79*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="J79" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K79" s="34" t="n">
+        <x:f>I79*J79</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="L79" s="30" t="str">
+        <x:v>原通信行 23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="23" customHeight="1">
+      <x:c r="A80" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B80" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C80" s="30" t="str">
+        <x:v>Attention 前</x:v>
+      </x:c>
+      <x:c r="D80" s="34" t="n">
+        <x:f>(K24*2^20)/1e9</x:f>
+        <x:v>0.06422528</x:v>
+      </x:c>
+      <x:c r="E80" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F80" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E80),E80&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F80),F80&gt;=0,F80&lt;=1,ISNUMBER(J80),J80&gt;=0,J80&lt;=1),D80/E80*1000,NA())</x:f>
+        <x:v>0.6422528</x:v>
+      </x:c>
+      <x:c r="H80" s="34" t="n">
+        <x:f>G80+I80</x:f>
+        <x:v>0.7136142222222221</x:v>
+      </x:c>
+      <x:c r="I80" s="34" t="n">
+        <x:f>G80*F80*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.07136142222222222</x:v>
+      </x:c>
+      <x:c r="J80" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K80" s="34" t="n">
+        <x:f>I80*J80</x:f>
+        <x:v>0.07136142222222222</x:v>
+      </x:c>
+      <x:c r="L80" s="30" t="str">
+        <x:v>原通信行 24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="23" customHeight="1">
+      <x:c r="A81" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B81" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C81" s="30" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D81" s="34" t="n">
+        <x:f>(K25*2^20)/1e9</x:f>
+        <x:v>0.06422528</x:v>
+      </x:c>
+      <x:c r="E81" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F81" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E81),E81&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F81),F81&gt;=0,F81&lt;=1,ISNUMBER(J81),J81&gt;=0,J81&lt;=1),D81/E81*1000,NA())</x:f>
+        <x:v>0.6422528</x:v>
+      </x:c>
+      <x:c r="H81" s="34" t="n">
+        <x:f>G81+I81</x:f>
+        <x:v>0.7136142222222221</x:v>
+      </x:c>
+      <x:c r="I81" s="34" t="n">
+        <x:f>G81*F81*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.07136142222222222</x:v>
+      </x:c>
+      <x:c r="J81" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K81" s="34" t="n">
+        <x:f>I81*J81</x:f>
+        <x:v>0.07136142222222222</x:v>
+      </x:c>
+      <x:c r="L81" s="30" t="str">
+        <x:v>原通信行 25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="23" customHeight="1">
+      <x:c r="A82" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B82" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C82" s="30" t="str">
+        <x:v>非 SP 标准 TP</x:v>
+      </x:c>
+      <x:c r="D82" s="34" t="n">
+        <x:f>(K26*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E82" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F82" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E82),E82&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F82),F82&gt;=0,F82&lt;=1,ISNUMBER(J82),J82&gt;=0,J82&lt;=1),D82/E82*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="34" t="n">
+        <x:f>G82+I82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I82" s="34" t="n">
+        <x:f>G82*F82*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J82" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K82" s="34" t="n">
+        <x:f>I82*J82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82" s="30" t="str">
+        <x:v>原通信行 26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="23" customHeight="1">
+      <x:c r="A83" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B83" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C83" s="30" t="str">
+        <x:v>O Proj 输入</x:v>
+      </x:c>
+      <x:c r="D83" s="34" t="n">
+        <x:f>(K27*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E83" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F83" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E83),E83&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F83),F83&gt;=0,F83&lt;=1,ISNUMBER(J83),J83&gt;=0,J83&lt;=1),D83/E83*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="34" t="n">
+        <x:f>G83+I83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I83" s="34" t="n">
+        <x:f>G83*F83*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J83" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K83" s="34" t="n">
+        <x:f>I83*J83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="30" t="str">
+        <x:v>原通信行 27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="23" customHeight="1">
+      <x:c r="A84" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B84" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="str">
+        <x:v>O Proj 输出</x:v>
+      </x:c>
+      <x:c r="D84" s="34" t="n">
+        <x:f>(K28*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E84" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F84" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E84),E84&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F84),F84&gt;=0,F84&lt;=1,ISNUMBER(J84),J84&gt;=0,J84&lt;=1),D84/E84*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="34" t="n">
+        <x:f>G84+I84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" s="34" t="n">
+        <x:f>G84*F84*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J84" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K84" s="34" t="n">
+        <x:f>I84*J84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L84" s="30" t="str">
+        <x:v>原通信行 28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="23" customHeight="1">
+      <x:c r="A85" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B85" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C85" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D85" s="34" t="n">
+        <x:f>(K29*2^20)/1e9</x:f>
+        <x:v>0.01605632</x:v>
+      </x:c>
+      <x:c r="E85" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F85" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E85),E85&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F85),F85&gt;=0,F85&lt;=1,ISNUMBER(J85),J85&gt;=0,J85&lt;=1),D85/E85*1000,NA())</x:f>
+        <x:v>0.1605632</x:v>
+      </x:c>
+      <x:c r="H85" s="34" t="n">
+        <x:f>G85+I85</x:f>
+        <x:v>0.17840355555555554</x:v>
+      </x:c>
+      <x:c r="I85" s="34" t="n">
+        <x:f>G85*F85*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.017840355555555555</x:v>
+      </x:c>
+      <x:c r="J85" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K85" s="34" t="n">
+        <x:f>I85*J85</x:f>
+        <x:v>0.017840355555555555</x:v>
+      </x:c>
+      <x:c r="L85" s="30" t="str">
+        <x:v>原通信行 29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="23" customHeight="1">
+      <x:c r="A86" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B86" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C86" s="30" t="str">
+        <x:v>Query</x:v>
+      </x:c>
+      <x:c r="D86" s="34" t="n">
+        <x:f>(K30*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E86" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F86" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E86),E86&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F86),F86&gt;=0,F86&lt;=1,ISNUMBER(J86),J86&gt;=0,J86&lt;=1),D86/E86*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="34" t="n">
+        <x:f>G86+I86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I86" s="34" t="n">
+        <x:f>G86*F86*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J86" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" s="34" t="n">
+        <x:f>I86*J86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="30" t="str">
+        <x:v>原通信行 30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="23" customHeight="1">
+      <x:c r="A87" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B87" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C87" s="30" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D87" s="34" t="n">
+        <x:f>(K31*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E87" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E87),E87&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F87),F87&gt;=0,F87&lt;=1,ISNUMBER(J87),J87&gt;=0,J87&lt;=1),D87/E87*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="34" t="n">
+        <x:f>G87+I87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I87" s="34" t="n">
+        <x:f>G87*F87*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J87" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K87" s="34" t="n">
+        <x:f>I87*J87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L87" s="30" t="str">
+        <x:v>原通信行 31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="23" customHeight="1">
+      <x:c r="A88" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B88" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C88" s="30" t="str">
+        <x:v>Attention 输出</x:v>
+      </x:c>
+      <x:c r="D88" s="34" t="n">
+        <x:f>(K32*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E88" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E88),E88&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F88),F88&gt;=0,F88&lt;=1,ISNUMBER(J88),J88&gt;=0,J88&lt;=1),D88/E88*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="34" t="n">
+        <x:f>G88+I88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="34" t="n">
+        <x:f>G88*F88*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K88" s="34" t="n">
+        <x:f>I88*J88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="30" t="str">
+        <x:v>原通信行 32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="23" customHeight="1">
+      <x:c r="A89" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B89" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C89" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D89" s="34" t="n">
+        <x:f>(K33*2^20)/1e9</x:f>
+        <x:v>0.012845056</x:v>
+      </x:c>
+      <x:c r="E89" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E89),E89&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F89),F89&gt;=0,F89&lt;=1,ISNUMBER(J89),J89&gt;=0,J89&lt;=1),D89/E89*1000,NA())</x:f>
+        <x:v>0.12845056000000002</x:v>
+      </x:c>
+      <x:c r="H89" s="34" t="n">
+        <x:f>G89+I89</x:f>
+        <x:v>0.14272284444444447</x:v>
+      </x:c>
+      <x:c r="I89" s="34" t="n">
+        <x:f>G89*F89*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="J89" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K89" s="34" t="n">
+        <x:f>I89*J89</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="L89" s="30" t="str">
+        <x:v>原通信行 33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="23" customHeight="1">
+      <x:c r="A90" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B90" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C90" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D90" s="34" t="n">
+        <x:f>(K34*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E90" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E90),E90&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F90),F90&gt;=0,F90&lt;=1,ISNUMBER(J90),J90&gt;=0,J90&lt;=1),D90/E90*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="34" t="n">
+        <x:f>G90+I90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" s="34" t="n">
+        <x:f>G90*F90*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J90" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K90" s="34" t="n">
+        <x:f>I90*J90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" s="30" t="str">
+        <x:v>原通信行 34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="23" customHeight="1">
+      <x:c r="A91" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B91" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D91" s="34" t="n">
+        <x:f>(K35*2^20)/1e9</x:f>
+        <x:v>0.011010048</x:v>
+      </x:c>
+      <x:c r="E91" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E91),E91&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F91),F91&gt;=0,F91&lt;=1,ISNUMBER(J91),J91&gt;=0,J91&lt;=1),D91/E91*1000,NA())</x:f>
+        <x:v>0.11010048</x:v>
+      </x:c>
+      <x:c r="H91" s="34" t="n">
+        <x:f>G91+I91</x:f>
+        <x:v>0.12233386666666667</x:v>
+      </x:c>
+      <x:c r="I91" s="34" t="n">
+        <x:f>G91*F91*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="J91" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K91" s="34" t="n">
+        <x:f>I91*J91</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="L91" s="30" t="str">
+        <x:v>原通信行 35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="23" customHeight="1">
+      <x:c r="A92" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B92" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D92" s="34" t="n">
+        <x:f>(K36*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E92" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E92),E92&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F92),F92&gt;=0,F92&lt;=1,ISNUMBER(J92),J92&gt;=0,J92&lt;=1),D92/E92*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="34" t="n">
+        <x:f>G92+I92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I92" s="34" t="n">
+        <x:f>G92*F92*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J92" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K92" s="34" t="n">
+        <x:f>I92*J92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L92" s="30" t="str">
+        <x:v>原通信行 36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="23" customHeight="1">
+      <x:c r="A93" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B93" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C93" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D93" s="34" t="n">
+        <x:f>(K37*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E93" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G93" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E93),E93&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F93),F93&gt;=0,F93&lt;=1,ISNUMBER(J93),J93&gt;=0,J93&lt;=1),D93/E93*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="34" t="n">
+        <x:f>G93+I93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I93" s="34" t="n">
+        <x:f>G93*F93*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J93" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K93" s="34" t="n">
+        <x:f>I93*J93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L93" s="30" t="str">
+        <x:v>原通信行 37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="23" customHeight="1">
+      <x:c r="A94" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B94" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C94" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D94" s="34" t="n">
+        <x:f>(K38*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E94" s="51" t="n">
+        <x:f>$H$73</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E94),E94&gt;0,ISNUMBER($B$73),$B$73&gt;=0,$B$73&lt;1,ISNUMBER($D$73),$D$73&gt;=0,$D$73&lt;=1,ISNUMBER(F94),F94&gt;=0,F94&lt;=1,ISNUMBER(J94),J94&gt;=0,J94&lt;=1),D94/E94*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="34" t="n">
+        <x:f>G94+I94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I94" s="34" t="n">
+        <x:f>G94*F94*$D$73*$B$73/(1-$B$73)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J94" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K94" s="34" t="n">
+        <x:f>I94*J94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L94" s="30" t="str">
+        <x:v>原通信行 38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="23" customHeight="1">
+      <x:c r="A95" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B95" s="53"/>
+      <x:c r="C95" s="53"/>
+      <x:c r="D95" s="54" t="n">
+        <x:f>SUM(D79:D94)</x:f>
+        <x:v>0.18120703999999996</x:v>
+      </x:c>
+      <x:c r="E95" s="54"/>
+      <x:c r="F95" s="53"/>
+      <x:c r="G95" s="54" t="n">
+        <x:f>SUM(G79:G94)</x:f>
+        <x:v>1.8120703999999999</x:v>
+      </x:c>
+      <x:c r="H95" s="54" t="n">
+        <x:f>SUM(H79:H94)</x:f>
+        <x:v>2.0134115555555554</x:v>
+      </x:c>
+      <x:c r="I95" s="54" t="n">
+        <x:f>SUM(I79:I94)</x:f>
+        <x:v>0.20134115555555557</x:v>
+      </x:c>
+      <x:c r="J95" s="53"/>
+      <x:c r="K95" s="54" t="n">
+        <x:f>SUM(K79:K94)</x:f>
+        <x:v>0.20134115555555557</x:v>
+      </x:c>
+      <x:c r="L95" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L75:L75">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/models/kimi-k3-dspark/kimi-k3-dspark-analysis.xlsx
+++ b/models/kimi-k3-dspark/kimi-k3-dspark-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R070dcea449ad466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rc7bfa200ed554920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R621feff213774b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rb0faa91357964671"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -124,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -236,6 +241,36 @@
     <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -246,7 +281,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -256,7 +291,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2221,8 +2256,8 @@
       <x:c r="O37" s="30"/>
       <x:c r="P37" s="30"/>
     </x:row>
-    <x:row r="70" ht="23" customHeight="1">
-      <x:c r="A70" s="42" t="str">
+    <x:row r="70" ht="15" customHeight="1">
+      <x:c r="A70" s="39" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B70" s="30"/>
@@ -2237,7 +2272,7 @@
       <x:c r="K70" s="30"/>
       <x:c r="L70" s="30"/>
     </x:row>
-    <x:row r="71" ht="23" customHeight="1">
+    <x:row r="71" ht="15" customHeight="1">
       <x:c r="A71" s="30" t="str">
         <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -2253,29 +2288,29 @@
       <x:c r="K71" s="30"/>
       <x:c r="L71" s="30"/>
     </x:row>
-    <x:row r="72" ht="38" customHeight="1">
-      <x:c r="A72" s="45" t="str">
+    <x:row r="72" ht="30" customHeight="1">
+      <x:c r="A72" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B72" s="45" t="str">
+      <x:c r="B72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C72" s="45" t="str">
+      <x:c r="C72" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D72" s="45" t="str">
+      <x:c r="D72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E72" s="45" t="str">
+      <x:c r="E72" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F72" s="45" t="str">
+      <x:c r="F72" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G72" s="45" t="str">
+      <x:c r="G72" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H72" s="45" t="str">
+      <x:c r="H72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I72" s="30"/>
@@ -2283,19 +2318,19 @@
       <x:c r="K72" s="30"/>
       <x:c r="L72" s="30"/>
     </x:row>
-    <x:row r="73" ht="23" customHeight="1">
+    <x:row r="73" ht="15" customHeight="1">
       <x:c r="A73" s="30"/>
-      <x:c r="B73" s="47" t="n">
+      <x:c r="B73" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C73" s="30"/>
-      <x:c r="D73" s="47" t="n">
+      <x:c r="D73" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E73" s="30"/>
-      <x:c r="F73" s="48"/>
+      <x:c r="F73" s="38"/>
       <x:c r="G73" s="30"/>
-      <x:c r="H73" s="48" t="n">
+      <x:c r="H73" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" s="30"/>
@@ -2303,45 +2338,45 @@
       <x:c r="K73" s="30"/>
       <x:c r="L73" s="30"/>
     </x:row>
-    <x:row r="74" ht="38" customHeight="1">
-      <x:c r="A74" s="45" t="str">
+    <x:row r="74" ht="30" customHeight="1">
+      <x:c r="A74" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B74" s="45" t="str">
+      <x:c r="B74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C74" s="45" t="str">
+      <x:c r="C74" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D74" s="45" t="str">
+      <x:c r="D74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E74" s="45" t="str">
+      <x:c r="E74" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F74" s="45" t="str">
+      <x:c r="F74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G74" s="45" t="str">
+      <x:c r="G74" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H74" s="45" t="str">
+      <x:c r="H74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I74" s="45" t="str">
+      <x:c r="I74" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J74" s="45" t="str">
+      <x:c r="J74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K74" s="45" t="str">
+      <x:c r="K74" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L74" s="45" t="str">
+      <x:c r="L74" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="23" customHeight="1">
+    <x:row r="75" ht="15" customHeight="1">
       <x:c r="A75" s="49"/>
       <x:c r="B75" s="49" t="n">
         <x:f>SUM(G79:G92)</x:f>
@@ -2371,7 +2406,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="23" customHeight="1">
+    <x:row r="76" ht="15" customHeight="1">
       <x:c r="A76" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -2387,7 +2422,7 @@
       <x:c r="K76" s="30"/>
       <x:c r="L76" s="30"/>
     </x:row>
-    <x:row r="77" ht="23" customHeight="1">
+    <x:row r="77" ht="15" customHeight="1">
       <x:c r="A77" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -2403,45 +2438,45 @@
       <x:c r="K77" s="30"/>
       <x:c r="L77" s="30"/>
     </x:row>
-    <x:row r="78" ht="38" customHeight="1">
-      <x:c r="A78" s="45" t="str">
+    <x:row r="78" ht="30" customHeight="1">
+      <x:c r="A78" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B78" s="45" t="str">
+      <x:c r="B78" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C78" s="45" t="str">
+      <x:c r="C78" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D78" s="45" t="str">
+      <x:c r="D78" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E78" s="45" t="str">
+      <x:c r="E78" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F78" s="45" t="str">
+      <x:c r="F78" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G78" s="45" t="str">
+      <x:c r="G78" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H78" s="45" t="str">
+      <x:c r="H78" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I78" s="45" t="str">
+      <x:c r="I78" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J78" s="45" t="str">
+      <x:c r="J78" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K78" s="45" t="str">
+      <x:c r="K78" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L78" s="45" t="str">
+      <x:c r="L78" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="23" customHeight="1">
+    <x:row r="79" ht="15" customHeight="1">
       <x:c r="A79" s="30" t="str">
         <x:v>TP</x:v>
       </x:c>
@@ -2455,11 +2490,11 @@
         <x:f>(K23*2^20)/1e9</x:f>
         <x:v>0.102760448</x:v>
       </x:c>
-      <x:c r="E79" s="51" t="n">
+      <x:c r="E79" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F79" s="52" t="n">
+      <x:c r="F79" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G79" s="34" t="n">
@@ -2474,7 +2509,7 @@
         <x:f>G79*F79*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.11417827555555557</x:v>
       </x:c>
-      <x:c r="J79" s="52" t="n">
+      <x:c r="J79" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K79" s="34" t="n">
@@ -2485,7 +2520,7 @@
         <x:v>原通信行 23</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="23" customHeight="1">
+    <x:row r="80" ht="15" customHeight="1">
       <x:c r="A80" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -2499,11 +2534,11 @@
         <x:f>(K24*2^20)/1e9</x:f>
         <x:v>0.51380224</x:v>
       </x:c>
-      <x:c r="E80" s="51" t="n">
+      <x:c r="E80" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F80" s="52" t="n">
+      <x:c r="F80" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G80" s="34" t="n">
@@ -2518,7 +2553,7 @@
         <x:f>G80*F80*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.5708913777777778</x:v>
       </x:c>
-      <x:c r="J80" s="52" t="n">
+      <x:c r="J80" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K80" s="34" t="n">
@@ -2529,7 +2564,7 @@
         <x:v>原通信行 24</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="23" customHeight="1">
+    <x:row r="81" ht="15" customHeight="1">
       <x:c r="A81" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -2543,11 +2578,11 @@
         <x:f>(K25*2^20)/1e9</x:f>
         <x:v>0.51380224</x:v>
       </x:c>
-      <x:c r="E81" s="51" t="n">
+      <x:c r="E81" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F81" s="52" t="n">
+      <x:c r="F81" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G81" s="34" t="n">
@@ -2562,7 +2597,7 @@
         <x:f>G81*F81*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.5708913777777778</x:v>
       </x:c>
-      <x:c r="J81" s="52" t="n">
+      <x:c r="J81" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K81" s="34" t="n">
@@ -2573,7 +2608,7 @@
         <x:v>原通信行 25</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="23" customHeight="1">
+    <x:row r="82" ht="15" customHeight="1">
       <x:c r="A82" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -2587,11 +2622,11 @@
         <x:f>(K26*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E82" s="51" t="n">
+      <x:c r="E82" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F82" s="52" t="n">
+      <x:c r="F82" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G82" s="34" t="n">
@@ -2606,7 +2641,7 @@
         <x:f>G82*F82*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J82" s="52" t="n">
+      <x:c r="J82" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K82" s="34" t="n">
@@ -2617,7 +2652,7 @@
         <x:v>原通信行 26</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="23" customHeight="1">
+    <x:row r="83" ht="15" customHeight="1">
       <x:c r="A83" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -2631,11 +2666,11 @@
         <x:f>(K27*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E83" s="51" t="n">
+      <x:c r="E83" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F83" s="52" t="n">
+      <x:c r="F83" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G83" s="34" t="n">
@@ -2650,7 +2685,7 @@
         <x:f>G83*F83*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J83" s="52" t="n">
+      <x:c r="J83" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K83" s="34" t="n">
@@ -2661,7 +2696,7 @@
         <x:v>原通信行 27</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="23" customHeight="1">
+    <x:row r="84" ht="15" customHeight="1">
       <x:c r="A84" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -2675,11 +2710,11 @@
         <x:f>(K28*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E84" s="51" t="n">
+      <x:c r="E84" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F84" s="52" t="n">
+      <x:c r="F84" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G84" s="34" t="n">
@@ -2694,7 +2729,7 @@
         <x:f>G84*F84*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J84" s="52" t="n">
+      <x:c r="J84" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K84" s="34" t="n">
@@ -2705,7 +2740,7 @@
         <x:v>原通信行 28</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="23" customHeight="1">
+    <x:row r="85" ht="15" customHeight="1">
       <x:c r="A85" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -2719,11 +2754,11 @@
         <x:f>(K29*2^20)/1e9</x:f>
         <x:v>0.12845056</x:v>
       </x:c>
-      <x:c r="E85" s="51" t="n">
+      <x:c r="E85" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F85" s="52" t="n">
+      <x:c r="F85" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G85" s="34" t="n">
@@ -2738,7 +2773,7 @@
         <x:f>G85*F85*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.14272284444444444</x:v>
       </x:c>
-      <x:c r="J85" s="52" t="n">
+      <x:c r="J85" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K85" s="34" t="n">
@@ -2749,7 +2784,7 @@
         <x:v>原通信行 29</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="23" customHeight="1">
+    <x:row r="86" ht="15" customHeight="1">
       <x:c r="A86" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -2763,11 +2798,11 @@
         <x:f>(K30*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E86" s="51" t="n">
+      <x:c r="E86" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F86" s="52" t="n">
+      <x:c r="F86" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G86" s="34" t="n">
@@ -2782,7 +2817,7 @@
         <x:f>G86*F86*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J86" s="52" t="n">
+      <x:c r="J86" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K86" s="34" t="n">
@@ -2793,7 +2828,7 @@
         <x:v>原通信行 30</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="23" customHeight="1">
+    <x:row r="87" ht="15" customHeight="1">
       <x:c r="A87" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -2807,11 +2842,11 @@
         <x:f>(K31*2^20)/1e9</x:f>
         <x:v>0.102760448</x:v>
       </x:c>
-      <x:c r="E87" s="51" t="n">
+      <x:c r="E87" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F87" s="52" t="n">
+      <x:c r="F87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G87" s="34" t="n">
@@ -2826,7 +2861,7 @@
         <x:f>G87*F87*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.11417827555555557</x:v>
       </x:c>
-      <x:c r="J87" s="52" t="n">
+      <x:c r="J87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K87" s="34" t="n">
@@ -2837,7 +2872,7 @@
         <x:v>原通信行 31</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="23" customHeight="1">
+    <x:row r="88" ht="15" customHeight="1">
       <x:c r="A88" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -2851,11 +2886,11 @@
         <x:f>(K32*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E88" s="51" t="n">
+      <x:c r="E88" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F88" s="52" t="n">
+      <x:c r="F88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G88" s="34" t="n">
@@ -2870,7 +2905,7 @@
         <x:f>G88*F88*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J88" s="52" t="n">
+      <x:c r="J88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K88" s="34" t="n">
@@ -2881,7 +2916,7 @@
         <x:v>原通信行 32</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="23" customHeight="1">
+    <x:row r="89" ht="15" customHeight="1">
       <x:c r="A89" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -2895,11 +2930,11 @@
         <x:f>(K33*2^20)/1e9</x:f>
         <x:v>0.001376256</x:v>
       </x:c>
-      <x:c r="E89" s="51" t="n">
+      <x:c r="E89" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F89" s="52" t="n">
+      <x:c r="F89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G89" s="34" t="n">
@@ -2914,7 +2949,7 @@
         <x:f>G89*F89*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.0015291733333333336</x:v>
       </x:c>
-      <x:c r="J89" s="52" t="n">
+      <x:c r="J89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K89" s="34" t="n">
@@ -2925,7 +2960,7 @@
         <x:v>原通信行 33</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="23" customHeight="1">
+    <x:row r="90" ht="15" customHeight="1">
       <x:c r="A90" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -2939,11 +2974,11 @@
         <x:f>(K34*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E90" s="51" t="n">
+      <x:c r="E90" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F90" s="52" t="n">
+      <x:c r="F90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G90" s="34" t="n">
@@ -2958,7 +2993,7 @@
         <x:f>G90*F90*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J90" s="52" t="n">
+      <x:c r="J90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K90" s="34" t="n">
@@ -2969,7 +3004,7 @@
         <x:v>原通信行 34</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="23" customHeight="1">
+    <x:row r="91" ht="15" customHeight="1">
       <x:c r="A91" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -2983,11 +3018,11 @@
         <x:f>(K35*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E91" s="51" t="n">
+      <x:c r="E91" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F91" s="52" t="n">
+      <x:c r="F91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G91" s="34" t="n">
@@ -3002,7 +3037,7 @@
         <x:f>G91*F91*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J91" s="52" t="n">
+      <x:c r="J91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K91" s="34" t="n">
@@ -3013,7 +3048,7 @@
         <x:v>原通信行 35</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="23" customHeight="1">
+    <x:row r="92" ht="15" customHeight="1">
       <x:c r="A92" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -3027,11 +3062,11 @@
         <x:f>(K36*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E92" s="51" t="n">
+      <x:c r="E92" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F92" s="52" t="n">
+      <x:c r="F92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G92" s="34" t="n">
@@ -3046,7 +3081,7 @@
         <x:f>G92*F92*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J92" s="52" t="n">
+      <x:c r="J92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K92" s="34" t="n">
@@ -3057,36 +3092,36 @@
         <x:v>原通信行 36</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="23" customHeight="1">
-      <x:c r="A93" s="53" t="str">
+    <x:row r="93" ht="15" customHeight="1">
+      <x:c r="A93" s="39" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B93" s="53"/>
-      <x:c r="C93" s="53"/>
-      <x:c r="D93" s="54" t="n">
+      <x:c r="B93" s="39"/>
+      <x:c r="C93" s="39"/>
+      <x:c r="D93" s="40" t="n">
         <x:f>SUM(D79:D92)</x:f>
         <x:v>1.3629521919999996</x:v>
       </x:c>
-      <x:c r="E93" s="54"/>
-      <x:c r="F93" s="53"/>
-      <x:c r="G93" s="54" t="n">
+      <x:c r="E93" s="39"/>
+      <x:c r="F93" s="39"/>
+      <x:c r="G93" s="40" t="n">
         <x:f>SUM(G79:G92)</x:f>
         <x:v>13.629521919999998</x:v>
       </x:c>
-      <x:c r="H93" s="54" t="n">
+      <x:c r="H93" s="40" t="n">
         <x:f>SUM(H79:H92)</x:f>
         <x:v>15.143913244444445</x:v>
       </x:c>
-      <x:c r="I93" s="54" t="n">
+      <x:c r="I93" s="40" t="n">
         <x:f>SUM(I79:I92)</x:f>
         <x:v>1.5143913244444445</x:v>
       </x:c>
-      <x:c r="J93" s="53"/>
-      <x:c r="K93" s="54" t="n">
+      <x:c r="J93" s="39"/>
+      <x:c r="K93" s="40" t="n">
         <x:f>SUM(K79:K92)</x:f>
         <x:v>1.5143913244444445</x:v>
       </x:c>
-      <x:c r="L93" s="53"/>
+      <x:c r="L93" s="39"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L75:L75">
@@ -4961,8 +4996,8 @@
       <x:c r="O39" s="30"/>
       <x:c r="P39" s="30"/>
     </x:row>
-    <x:row r="70" ht="23" customHeight="1">
-      <x:c r="A70" s="42" t="str">
+    <x:row r="70" ht="15" customHeight="1">
+      <x:c r="A70" s="39" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B70" s="30"/>
@@ -4977,7 +5012,7 @@
       <x:c r="K70" s="30"/>
       <x:c r="L70" s="30"/>
     </x:row>
-    <x:row r="71" ht="23" customHeight="1">
+    <x:row r="71" ht="15" customHeight="1">
       <x:c r="A71" s="30" t="str">
         <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -4993,29 +5028,29 @@
       <x:c r="K71" s="30"/>
       <x:c r="L71" s="30"/>
     </x:row>
-    <x:row r="72" ht="38" customHeight="1">
-      <x:c r="A72" s="45" t="str">
+    <x:row r="72" ht="30" customHeight="1">
+      <x:c r="A72" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B72" s="45" t="str">
+      <x:c r="B72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C72" s="45" t="str">
+      <x:c r="C72" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D72" s="45" t="str">
+      <x:c r="D72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E72" s="45" t="str">
+      <x:c r="E72" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F72" s="45" t="str">
+      <x:c r="F72" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G72" s="45" t="str">
+      <x:c r="G72" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H72" s="45" t="str">
+      <x:c r="H72" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I72" s="30"/>
@@ -5023,19 +5058,19 @@
       <x:c r="K72" s="30"/>
       <x:c r="L72" s="30"/>
     </x:row>
-    <x:row r="73" ht="23" customHeight="1">
+    <x:row r="73" ht="15" customHeight="1">
       <x:c r="A73" s="30"/>
-      <x:c r="B73" s="47" t="n">
+      <x:c r="B73" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C73" s="30"/>
-      <x:c r="D73" s="47" t="n">
+      <x:c r="D73" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E73" s="30"/>
-      <x:c r="F73" s="48"/>
+      <x:c r="F73" s="38"/>
       <x:c r="G73" s="30"/>
-      <x:c r="H73" s="48" t="n">
+      <x:c r="H73" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" s="30"/>
@@ -5043,45 +5078,45 @@
       <x:c r="K73" s="30"/>
       <x:c r="L73" s="30"/>
     </x:row>
-    <x:row r="74" ht="38" customHeight="1">
-      <x:c r="A74" s="45" t="str">
+    <x:row r="74" ht="30" customHeight="1">
+      <x:c r="A74" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B74" s="45" t="str">
+      <x:c r="B74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C74" s="45" t="str">
+      <x:c r="C74" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D74" s="45" t="str">
+      <x:c r="D74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E74" s="45" t="str">
+      <x:c r="E74" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F74" s="45" t="str">
+      <x:c r="F74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G74" s="45" t="str">
+      <x:c r="G74" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H74" s="45" t="str">
+      <x:c r="H74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I74" s="45" t="str">
+      <x:c r="I74" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J74" s="45" t="str">
+      <x:c r="J74" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K74" s="45" t="str">
+      <x:c r="K74" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L74" s="45" t="str">
+      <x:c r="L74" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="23" customHeight="1">
+    <x:row r="75" ht="15" customHeight="1">
       <x:c r="A75" s="49"/>
       <x:c r="B75" s="49" t="n">
         <x:f>SUM(G79:G94)</x:f>
@@ -5111,7 +5146,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="23" customHeight="1">
+    <x:row r="76" ht="15" customHeight="1">
       <x:c r="A76" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -5127,7 +5162,7 @@
       <x:c r="K76" s="30"/>
       <x:c r="L76" s="30"/>
     </x:row>
-    <x:row r="77" ht="23" customHeight="1">
+    <x:row r="77" ht="15" customHeight="1">
       <x:c r="A77" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -5143,45 +5178,45 @@
       <x:c r="K77" s="30"/>
       <x:c r="L77" s="30"/>
     </x:row>
-    <x:row r="78" ht="38" customHeight="1">
-      <x:c r="A78" s="45" t="str">
+    <x:row r="78" ht="30" customHeight="1">
+      <x:c r="A78" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B78" s="45" t="str">
+      <x:c r="B78" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C78" s="45" t="str">
+      <x:c r="C78" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D78" s="45" t="str">
+      <x:c r="D78" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E78" s="45" t="str">
+      <x:c r="E78" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F78" s="45" t="str">
+      <x:c r="F78" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G78" s="45" t="str">
+      <x:c r="G78" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H78" s="45" t="str">
+      <x:c r="H78" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I78" s="45" t="str">
+      <x:c r="I78" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J78" s="45" t="str">
+      <x:c r="J78" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K78" s="45" t="str">
+      <x:c r="K78" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L78" s="45" t="str">
+      <x:c r="L78" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="23" customHeight="1">
+    <x:row r="79" ht="15" customHeight="1">
       <x:c r="A79" s="30" t="str">
         <x:v>TP</x:v>
       </x:c>
@@ -5195,11 +5230,11 @@
         <x:f>(K23*2^20)/1e9</x:f>
         <x:v>0.012845056</x:v>
       </x:c>
-      <x:c r="E79" s="51" t="n">
+      <x:c r="E79" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F79" s="52" t="n">
+      <x:c r="F79" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G79" s="34" t="n">
@@ -5214,7 +5249,7 @@
         <x:f>G79*F79*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.014272284444444446</x:v>
       </x:c>
-      <x:c r="J79" s="52" t="n">
+      <x:c r="J79" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K79" s="34" t="n">
@@ -5225,7 +5260,7 @@
         <x:v>原通信行 23</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="23" customHeight="1">
+    <x:row r="80" ht="15" customHeight="1">
       <x:c r="A80" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5239,11 +5274,11 @@
         <x:f>(K24*2^20)/1e9</x:f>
         <x:v>0.06422528</x:v>
       </x:c>
-      <x:c r="E80" s="51" t="n">
+      <x:c r="E80" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F80" s="52" t="n">
+      <x:c r="F80" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G80" s="34" t="n">
@@ -5258,7 +5293,7 @@
         <x:f>G80*F80*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.07136142222222222</x:v>
       </x:c>
-      <x:c r="J80" s="52" t="n">
+      <x:c r="J80" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K80" s="34" t="n">
@@ -5269,7 +5304,7 @@
         <x:v>原通信行 24</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="23" customHeight="1">
+    <x:row r="81" ht="15" customHeight="1">
       <x:c r="A81" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5283,11 +5318,11 @@
         <x:f>(K25*2^20)/1e9</x:f>
         <x:v>0.06422528</x:v>
       </x:c>
-      <x:c r="E81" s="51" t="n">
+      <x:c r="E81" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F81" s="52" t="n">
+      <x:c r="F81" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G81" s="34" t="n">
@@ -5302,7 +5337,7 @@
         <x:f>G81*F81*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.07136142222222222</x:v>
       </x:c>
-      <x:c r="J81" s="52" t="n">
+      <x:c r="J81" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K81" s="34" t="n">
@@ -5313,7 +5348,7 @@
         <x:v>原通信行 25</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="23" customHeight="1">
+    <x:row r="82" ht="15" customHeight="1">
       <x:c r="A82" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -5327,11 +5362,11 @@
         <x:f>(K26*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E82" s="51" t="n">
+      <x:c r="E82" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F82" s="52" t="n">
+      <x:c r="F82" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G82" s="34" t="n">
@@ -5346,7 +5381,7 @@
         <x:f>G82*F82*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J82" s="52" t="n">
+      <x:c r="J82" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K82" s="34" t="n">
@@ -5357,7 +5392,7 @@
         <x:v>原通信行 26</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="23" customHeight="1">
+    <x:row r="83" ht="15" customHeight="1">
       <x:c r="A83" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -5371,11 +5406,11 @@
         <x:f>(K27*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E83" s="51" t="n">
+      <x:c r="E83" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F83" s="52" t="n">
+      <x:c r="F83" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G83" s="34" t="n">
@@ -5390,7 +5425,7 @@
         <x:f>G83*F83*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J83" s="52" t="n">
+      <x:c r="J83" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K83" s="34" t="n">
@@ -5401,7 +5436,7 @@
         <x:v>原通信行 27</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="23" customHeight="1">
+    <x:row r="84" ht="15" customHeight="1">
       <x:c r="A84" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -5415,11 +5450,11 @@
         <x:f>(K28*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E84" s="51" t="n">
+      <x:c r="E84" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F84" s="52" t="n">
+      <x:c r="F84" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G84" s="34" t="n">
@@ -5434,7 +5469,7 @@
         <x:f>G84*F84*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J84" s="52" t="n">
+      <x:c r="J84" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K84" s="34" t="n">
@@ -5445,7 +5480,7 @@
         <x:v>原通信行 28</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="23" customHeight="1">
+    <x:row r="85" ht="15" customHeight="1">
       <x:c r="A85" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5459,11 +5494,11 @@
         <x:f>(K29*2^20)/1e9</x:f>
         <x:v>0.01605632</x:v>
       </x:c>
-      <x:c r="E85" s="51" t="n">
+      <x:c r="E85" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F85" s="52" t="n">
+      <x:c r="F85" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G85" s="34" t="n">
@@ -5478,7 +5513,7 @@
         <x:f>G85*F85*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.017840355555555555</x:v>
       </x:c>
-      <x:c r="J85" s="52" t="n">
+      <x:c r="J85" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K85" s="34" t="n">
@@ -5489,7 +5524,7 @@
         <x:v>原通信行 29</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="23" customHeight="1">
+    <x:row r="86" ht="15" customHeight="1">
       <x:c r="A86" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -5503,11 +5538,11 @@
         <x:f>(K30*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E86" s="51" t="n">
+      <x:c r="E86" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F86" s="52" t="n">
+      <x:c r="F86" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G86" s="34" t="n">
@@ -5522,7 +5557,7 @@
         <x:f>G86*F86*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J86" s="52" t="n">
+      <x:c r="J86" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K86" s="34" t="n">
@@ -5533,7 +5568,7 @@
         <x:v>原通信行 30</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="23" customHeight="1">
+    <x:row r="87" ht="15" customHeight="1">
       <x:c r="A87" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -5547,11 +5582,11 @@
         <x:f>(K31*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E87" s="51" t="n">
+      <x:c r="E87" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F87" s="52" t="n">
+      <x:c r="F87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G87" s="34" t="n">
@@ -5566,7 +5601,7 @@
         <x:f>G87*F87*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J87" s="52" t="n">
+      <x:c r="J87" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K87" s="34" t="n">
@@ -5577,7 +5612,7 @@
         <x:v>原通信行 31</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="23" customHeight="1">
+    <x:row r="88" ht="15" customHeight="1">
       <x:c r="A88" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -5591,11 +5626,11 @@
         <x:f>(K32*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E88" s="51" t="n">
+      <x:c r="E88" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F88" s="52" t="n">
+      <x:c r="F88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G88" s="34" t="n">
@@ -5610,7 +5645,7 @@
         <x:f>G88*F88*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J88" s="52" t="n">
+      <x:c r="J88" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K88" s="34" t="n">
@@ -5621,7 +5656,7 @@
         <x:v>原通信行 32</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="23" customHeight="1">
+    <x:row r="89" ht="15" customHeight="1">
       <x:c r="A89" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5635,11 +5670,11 @@
         <x:f>(K33*2^20)/1e9</x:f>
         <x:v>0.012845056</x:v>
       </x:c>
-      <x:c r="E89" s="51" t="n">
+      <x:c r="E89" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F89" s="52" t="n">
+      <x:c r="F89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G89" s="34" t="n">
@@ -5654,7 +5689,7 @@
         <x:f>G89*F89*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.014272284444444446</x:v>
       </x:c>
-      <x:c r="J89" s="52" t="n">
+      <x:c r="J89" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K89" s="34" t="n">
@@ -5665,7 +5700,7 @@
         <x:v>原通信行 33</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="23" customHeight="1">
+    <x:row r="90" ht="15" customHeight="1">
       <x:c r="A90" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5679,11 +5714,11 @@
         <x:f>(K34*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E90" s="51" t="n">
+      <x:c r="E90" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F90" s="52" t="n">
+      <x:c r="F90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G90" s="34" t="n">
@@ -5698,7 +5733,7 @@
         <x:f>G90*F90*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J90" s="52" t="n">
+      <x:c r="J90" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K90" s="34" t="n">
@@ -5709,7 +5744,7 @@
         <x:v>原通信行 34</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="23" customHeight="1">
+    <x:row r="91" ht="15" customHeight="1">
       <x:c r="A91" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5723,11 +5758,11 @@
         <x:f>(K35*2^20)/1e9</x:f>
         <x:v>0.011010048</x:v>
       </x:c>
-      <x:c r="E91" s="51" t="n">
+      <x:c r="E91" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F91" s="52" t="n">
+      <x:c r="F91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G91" s="34" t="n">
@@ -5742,7 +5777,7 @@
         <x:f>G91*F91*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0.012233386666666669</x:v>
       </x:c>
-      <x:c r="J91" s="52" t="n">
+      <x:c r="J91" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K91" s="34" t="n">
@@ -5753,7 +5788,7 @@
         <x:v>原通信行 35</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="23" customHeight="1">
+    <x:row r="92" ht="15" customHeight="1">
       <x:c r="A92" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5767,11 +5802,11 @@
         <x:f>(K36*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E92" s="51" t="n">
+      <x:c r="E92" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F92" s="52" t="n">
+      <x:c r="F92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G92" s="34" t="n">
@@ -5786,7 +5821,7 @@
         <x:f>G92*F92*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J92" s="52" t="n">
+      <x:c r="J92" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K92" s="34" t="n">
@@ -5797,7 +5832,7 @@
         <x:v>原通信行 36</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="23" customHeight="1">
+    <x:row r="93" ht="15" customHeight="1">
       <x:c r="A93" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5811,11 +5846,11 @@
         <x:f>(K37*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E93" s="51" t="n">
+      <x:c r="E93" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F93" s="52" t="n">
+      <x:c r="F93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G93" s="34" t="n">
@@ -5830,7 +5865,7 @@
         <x:f>G93*F93*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J93" s="52" t="n">
+      <x:c r="J93" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K93" s="34" t="n">
@@ -5841,7 +5876,7 @@
         <x:v>原通信行 37</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="23" customHeight="1">
+    <x:row r="94" ht="15" customHeight="1">
       <x:c r="A94" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5855,11 +5890,11 @@
         <x:f>(K38*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E94" s="51" t="n">
+      <x:c r="E94" s="64" t="n">
         <x:f>$H$73</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F94" s="52" t="n">
+      <x:c r="F94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G94" s="34" t="n">
@@ -5874,7 +5909,7 @@
         <x:f>G94*F94*$D$73*$B$73/(1-$B$73)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J94" s="52" t="n">
+      <x:c r="J94" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K94" s="34" t="n">
@@ -5885,36 +5920,36 @@
         <x:v>原通信行 38</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="23" customHeight="1">
-      <x:c r="A95" s="53" t="str">
+    <x:row r="95" ht="15" customHeight="1">
+      <x:c r="A95" s="39" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B95" s="53"/>
-      <x:c r="C95" s="53"/>
-      <x:c r="D95" s="54" t="n">
+      <x:c r="B95" s="39"/>
+      <x:c r="C95" s="39"/>
+      <x:c r="D95" s="40" t="n">
         <x:f>SUM(D79:D94)</x:f>
         <x:v>0.18120703999999996</x:v>
       </x:c>
-      <x:c r="E95" s="54"/>
-      <x:c r="F95" s="53"/>
-      <x:c r="G95" s="54" t="n">
+      <x:c r="E95" s="39"/>
+      <x:c r="F95" s="39"/>
+      <x:c r="G95" s="40" t="n">
         <x:f>SUM(G79:G94)</x:f>
         <x:v>1.8120703999999999</x:v>
       </x:c>
-      <x:c r="H95" s="54" t="n">
+      <x:c r="H95" s="40" t="n">
         <x:f>SUM(H79:H94)</x:f>
         <x:v>2.0134115555555554</x:v>
       </x:c>
-      <x:c r="I95" s="54" t="n">
+      <x:c r="I95" s="40" t="n">
         <x:f>SUM(I79:I94)</x:f>
         <x:v>0.20134115555555557</x:v>
       </x:c>
-      <x:c r="J95" s="53"/>
-      <x:c r="K95" s="54" t="n">
+      <x:c r="J95" s="39"/>
+      <x:c r="K95" s="40" t="n">
         <x:f>SUM(K79:K94)</x:f>
         <x:v>0.20134115555555557</x:v>
       </x:c>
-      <x:c r="L95" s="53"/>
+      <x:c r="L95" s="39"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L75:L75">
